--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -31,10 +31,10 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>System Validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC001: Verify backend service health </t>
+    <t>MAHIQ Database</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC001: Verify order insertion into MongoDB collection </t>
   </si>
   <si>
     <t>PASS</t>
@@ -43,907 +43,907 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:01:40 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC002: Verify database connection </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC003: Verify redis cache hit rate </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC004: Verify environment variables </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC005: Verify server memory limits </t>
-  </si>
-  <si>
-    <t>TC006: Verify backend service health (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC007: Verify database connection (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC008: Verify redis cache hit rate (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC009: Verify environment variables (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC010: Verify server memory limits (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC011: Verify backend service health (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC012: Verify database connection (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC013: Verify redis cache hit rate (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC014: Verify environment variables (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC015: Verify server memory limits (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC016: Verify backend service health (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC017: Verify database connection (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC018: Verify redis cache hit rate (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC019: Verify environment variables (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC020: Verify server memory limits (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC021: Verify backend service health (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC022: Verify database connection (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC023: Verify redis cache hit rate (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC024: Verify environment variables (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC025: Verify server memory limits (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC026: Verify backend service health (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC027: Verify database connection (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC028: Verify redis cache hit rate (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC029: Verify environment variables (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC030: Verify server memory limits (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC031: Verify backend service health (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC032: Verify database connection (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC033: Verify redis cache hit rate (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC034: Verify environment variables (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC035: Verify server memory limits (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC036: Verify backend service health (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC037: Verify database connection (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC038: Verify redis cache hit rate (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC039: Verify environment variables (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC040: Verify server memory limits (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC041: Verify backend service health (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC042: Verify database connection (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC043: Verify redis cache hit rate (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC044: Verify environment variables (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC045: Verify server memory limits (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC046: Verify backend service health (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC047: Verify database connection (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC048: Verify redis cache hit rate (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC049: Verify environment variables (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC050: Verify server memory limits (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC051: Verify backend service health (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC052: Verify database connection (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC053: Verify redis cache hit rate (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC054: Verify environment variables (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC055: Verify server memory limits (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC056: Verify backend service health (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC057: Verify database connection (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC058: Verify redis cache hit rate (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC059: Verify environment variables (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC060: Verify server memory limits (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC061: Verify backend service health (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC062: Verify database connection (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC063: Verify redis cache hit rate (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC064: Verify environment variables (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC065: Verify server memory limits (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC066: Verify backend service health (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC067: Verify database connection (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC068: Verify redis cache hit rate (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC069: Verify environment variables (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC070: Verify server memory limits (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC071: Verify backend service health (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC072: Verify database connection (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC073: Verify redis cache hit rate (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC074: Verify environment variables (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC075: Verify server memory limits (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC076: Verify backend service health (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC077: Verify database connection (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC078: Verify redis cache hit rate (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC079: Verify environment variables (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC080: Verify server memory limits (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC081: Verify backend service health (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC082: Verify database connection (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC083: Verify redis cache hit rate (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC084: Verify environment variables (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC085: Verify server memory limits (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC086: Verify backend service health (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC087: Verify database connection (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC088: Verify redis cache hit rate (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC089: Verify environment variables (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC090: Verify server memory limits (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC091: Verify backend service health (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC092: Verify database connection (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC093: Verify redis cache hit rate (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC094: Verify environment variables (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC095: Verify server memory limits (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC096: Verify backend service health (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC097: Verify database connection (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC098: Verify redis cache hit rate (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC099: Verify environment variables (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC100: Verify server memory limits (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC101: Verify backend service health (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC102: Verify database connection (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC103: Verify redis cache hit rate (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC104: Verify environment variables (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC105: Verify server memory limits (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC106: Verify backend service health (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC107: Verify database connection (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC108: Verify redis cache hit rate (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC109: Verify environment variables (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC110: Verify server memory limits (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC111: Verify backend service health (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC112: Verify database connection (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC113: Verify redis cache hit rate (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC114: Verify environment variables (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC115: Verify server memory limits (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC116: Verify backend service health (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC117: Verify database connection (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC118: Verify redis cache hit rate (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC119: Verify environment variables (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC120: Verify server memory limits (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC121: Verify backend service health (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC122: Verify database connection (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC123: Verify redis cache hit rate (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC124: Verify environment variables (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC125: Verify server memory limits (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC126: Verify backend service health (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC127: Verify database connection (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC128: Verify redis cache hit rate (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC129: Verify environment variables (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC130: Verify server memory limits (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC131: Verify backend service health (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC132: Verify database connection (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC133: Verify redis cache hit rate (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC134: Verify environment variables (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC135: Verify server memory limits (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC136: Verify backend service health (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC137: Verify database connection (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC138: Verify redis cache hit rate (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC139: Verify environment variables (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC140: Verify server memory limits (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC141: Verify backend service health (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC142: Verify database connection (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC143: Verify redis cache hit rate (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC144: Verify environment variables (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC145: Verify server memory limits (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC146: Verify backend service health (Scenario 30)</t>
-  </si>
-  <si>
-    <t>TC147: Verify database connection (Scenario 30)</t>
-  </si>
-  <si>
-    <t>TC148: Verify redis cache hit rate (Scenario 30)</t>
-  </si>
-  <si>
-    <t>TC149: Verify environment variables (Scenario 30)</t>
-  </si>
-  <si>
-    <t>TC150: Verify server memory limits (Scenario 30)</t>
-  </si>
-  <si>
-    <t>Integration Checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC151: Verify third-party payment gateway </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC152: Verify email service SMTP </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC153: Verify SMS OTP provider </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC154: Verify analytics tracking </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC155: Verify cloud storage upload </t>
-  </si>
-  <si>
-    <t>TC156: Verify third-party payment gateway (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC157: Verify email service SMTP (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC158: Verify SMS OTP provider (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC159: Verify analytics tracking (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC160: Verify cloud storage upload (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC161: Verify third-party payment gateway (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC162: Verify email service SMTP (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC163: Verify SMS OTP provider (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC164: Verify analytics tracking (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC165: Verify cloud storage upload (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC166: Verify third-party payment gateway (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC167: Verify email service SMTP (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC168: Verify SMS OTP provider (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC169: Verify analytics tracking (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC170: Verify cloud storage upload (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC171: Verify third-party payment gateway (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC172: Verify email service SMTP (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC173: Verify SMS OTP provider (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC174: Verify analytics tracking (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC175: Verify cloud storage upload (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC176: Verify third-party payment gateway (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC177: Verify email service SMTP (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC178: Verify SMS OTP provider (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC179: Verify analytics tracking (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC180: Verify cloud storage upload (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC181: Verify third-party payment gateway (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC182: Verify email service SMTP (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC183: Verify SMS OTP provider (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC184: Verify analytics tracking (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC185: Verify cloud storage upload (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC186: Verify third-party payment gateway (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC187: Verify email service SMTP (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC188: Verify SMS OTP provider (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC189: Verify analytics tracking (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC190: Verify cloud storage upload (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC191: Verify third-party payment gateway (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC192: Verify email service SMTP (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC193: Verify SMS OTP provider (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC194: Verify analytics tracking (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC195: Verify cloud storage upload (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC196: Verify third-party payment gateway (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC197: Verify email service SMTP (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC198: Verify SMS OTP provider (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC199: Verify analytics tracking (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC200: Verify cloud storage upload (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC201: Verify third-party payment gateway (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC202: Verify email service SMTP (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC203: Verify SMS OTP provider (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC204: Verify analytics tracking (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC205: Verify cloud storage upload (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC206: Verify third-party payment gateway (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC207: Verify email service SMTP (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC208: Verify SMS OTP provider (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC209: Verify analytics tracking (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC210: Verify cloud storage upload (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC211: Verify third-party payment gateway (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC212: Verify email service SMTP (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC213: Verify SMS OTP provider (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC214: Verify analytics tracking (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC215: Verify cloud storage upload (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC216: Verify third-party payment gateway (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC217: Verify email service SMTP (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC218: Verify SMS OTP provider (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC219: Verify analytics tracking (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC220: Verify cloud storage upload (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC221: Verify third-party payment gateway (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC222: Verify email service SMTP (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC223: Verify SMS OTP provider (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC224: Verify analytics tracking (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC225: Verify cloud storage upload (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC226: Verify third-party payment gateway (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC227: Verify email service SMTP (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC228: Verify SMS OTP provider (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC229: Verify analytics tracking (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC230: Verify cloud storage upload (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC231: Verify third-party payment gateway (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC232: Verify email service SMTP (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC233: Verify SMS OTP provider (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC234: Verify analytics tracking (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC235: Verify cloud storage upload (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC236: Verify third-party payment gateway (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC237: Verify email service SMTP (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC238: Verify SMS OTP provider (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC239: Verify analytics tracking (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC240: Verify cloud storage upload (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC241: Verify third-party payment gateway (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC242: Verify email service SMTP (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC243: Verify SMS OTP provider (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC244: Verify analytics tracking (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC245: Verify cloud storage upload (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC246: Verify third-party payment gateway (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC247: Verify email service SMTP (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC248: Verify SMS OTP provider (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC249: Verify analytics tracking (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC250: Verify cloud storage upload (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC251: Verify third-party payment gateway (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC252: Verify email service SMTP (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC253: Verify SMS OTP provider (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC254: Verify analytics tracking (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC255: Verify cloud storage upload (Scenario 21)</t>
-  </si>
-  <si>
-    <t>TC256: Verify third-party payment gateway (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC257: Verify email service SMTP (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC258: Verify SMS OTP provider (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC259: Verify analytics tracking (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC260: Verify cloud storage upload (Scenario 22)</t>
-  </si>
-  <si>
-    <t>TC261: Verify third-party payment gateway (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC262: Verify email service SMTP (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC263: Verify SMS OTP provider (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC264: Verify analytics tracking (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC265: Verify cloud storage upload (Scenario 23)</t>
-  </si>
-  <si>
-    <t>TC266: Verify third-party payment gateway (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC267: Verify email service SMTP (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC268: Verify SMS OTP provider (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC269: Verify analytics tracking (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC270: Verify cloud storage upload (Scenario 24)</t>
-  </si>
-  <si>
-    <t>TC271: Verify third-party payment gateway (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC272: Verify email service SMTP (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC273: Verify SMS OTP provider (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC274: Verify analytics tracking (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC275: Verify cloud storage upload (Scenario 25)</t>
-  </si>
-  <si>
-    <t>TC276: Verify third-party payment gateway (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC277: Verify email service SMTP (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC278: Verify SMS OTP provider (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC279: Verify analytics tracking (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC280: Verify cloud storage upload (Scenario 26)</t>
-  </si>
-  <si>
-    <t>TC281: Verify third-party payment gateway (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC282: Verify email service SMTP (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC283: Verify SMS OTP provider (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC284: Verify analytics tracking (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC285: Verify cloud storage upload (Scenario 27)</t>
-  </si>
-  <si>
-    <t>TC286: Verify third-party payment gateway (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC287: Verify email service SMTP (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC288: Verify SMS OTP provider (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC289: Verify analytics tracking (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC290: Verify cloud storage upload (Scenario 28)</t>
-  </si>
-  <si>
-    <t>TC291: Verify third-party payment gateway (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC292: Verify email service SMTP (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC293: Verify SMS OTP provider (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC294: Verify analytics tracking (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC295: Verify cloud storage upload (Scenario 29)</t>
-  </si>
-  <si>
-    <t>TC296: Verify third-party payment gateway (Scenario 30)</t>
-  </si>
-  <si>
-    <t>TC297: Verify email service SMTP (Scenario 30)</t>
-  </si>
-  <si>
-    <t>TC298: Verify SMS OTP provider (Scenario 30)</t>
-  </si>
-  <si>
-    <t>TC299: Verify analytics tracking (Scenario 30)</t>
-  </si>
-  <si>
-    <t>TC300: Verify cloud storage upload (Scenario 30)</t>
+    <t>8/7/2026, 4:12:20 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC003: Verify ACID transaction during concurrent order placement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC004: Verify database index on order_id for fast lookups </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC005: Verify daily backup job executes successfully </t>
+  </si>
+  <si>
+    <t>TC006: Verify order insertion into MongoDB collection (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC007: Verify Redis cache stores active menu items (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC008: Verify ACID transaction during concurrent order placement (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC009: Verify database index on order_id for fast lookups (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC010: Verify daily backup job executes successfully (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC011: Verify order insertion into MongoDB collection (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC012: Verify Redis cache stores active menu items (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC013: Verify ACID transaction during concurrent order placement (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC014: Verify database index on order_id for fast lookups (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC015: Verify daily backup job executes successfully (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC016: Verify order insertion into MongoDB collection (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC017: Verify Redis cache stores active menu items (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC018: Verify ACID transaction during concurrent order placement (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC019: Verify database index on order_id for fast lookups (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC020: Verify daily backup job executes successfully (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC021: Verify order insertion into MongoDB collection (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC022: Verify Redis cache stores active menu items (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC023: Verify ACID transaction during concurrent order placement (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC024: Verify database index on order_id for fast lookups (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC025: Verify daily backup job executes successfully (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC026: Verify order insertion into MongoDB collection (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC027: Verify Redis cache stores active menu items (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC028: Verify ACID transaction during concurrent order placement (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC029: Verify database index on order_id for fast lookups (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC030: Verify daily backup job executes successfully (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC031: Verify order insertion into MongoDB collection (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC032: Verify Redis cache stores active menu items (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC033: Verify ACID transaction during concurrent order placement (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC034: Verify database index on order_id for fast lookups (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC035: Verify daily backup job executes successfully (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC036: Verify order insertion into MongoDB collection (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC037: Verify Redis cache stores active menu items (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC038: Verify ACID transaction during concurrent order placement (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC039: Verify database index on order_id for fast lookups (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC040: Verify daily backup job executes successfully (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC041: Verify order insertion into MongoDB collection (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC042: Verify Redis cache stores active menu items (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC043: Verify ACID transaction during concurrent order placement (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC044: Verify database index on order_id for fast lookups (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC045: Verify daily backup job executes successfully (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC046: Verify order insertion into MongoDB collection (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC047: Verify Redis cache stores active menu items (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC048: Verify ACID transaction during concurrent order placement (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC049: Verify database index on order_id for fast lookups (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC050: Verify daily backup job executes successfully (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC051: Verify order insertion into MongoDB collection (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC052: Verify Redis cache stores active menu items (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC053: Verify ACID transaction during concurrent order placement (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC054: Verify database index on order_id for fast lookups (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC055: Verify daily backup job executes successfully (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC056: Verify order insertion into MongoDB collection (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC057: Verify Redis cache stores active menu items (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC058: Verify ACID transaction during concurrent order placement (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC059: Verify database index on order_id for fast lookups (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC060: Verify daily backup job executes successfully (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC061: Verify order insertion into MongoDB collection (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC062: Verify Redis cache stores active menu items (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC063: Verify ACID transaction during concurrent order placement (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC064: Verify database index on order_id for fast lookups (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC065: Verify daily backup job executes successfully (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC066: Verify order insertion into MongoDB collection (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC067: Verify Redis cache stores active menu items (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC068: Verify ACID transaction during concurrent order placement (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC069: Verify database index on order_id for fast lookups (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC070: Verify daily backup job executes successfully (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC071: Verify order insertion into MongoDB collection (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC072: Verify Redis cache stores active menu items (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC073: Verify ACID transaction during concurrent order placement (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC074: Verify database index on order_id for fast lookups (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC075: Verify daily backup job executes successfully (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC076: Verify order insertion into MongoDB collection (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC077: Verify Redis cache stores active menu items (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC078: Verify ACID transaction during concurrent order placement (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC079: Verify database index on order_id for fast lookups (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC080: Verify daily backup job executes successfully (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC081: Verify order insertion into MongoDB collection (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC082: Verify Redis cache stores active menu items (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC083: Verify ACID transaction during concurrent order placement (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC084: Verify database index on order_id for fast lookups (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC085: Verify daily backup job executes successfully (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC086: Verify order insertion into MongoDB collection (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC087: Verify Redis cache stores active menu items (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC088: Verify ACID transaction during concurrent order placement (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC089: Verify database index on order_id for fast lookups (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC090: Verify daily backup job executes successfully (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC091: Verify order insertion into MongoDB collection (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC092: Verify Redis cache stores active menu items (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC093: Verify ACID transaction during concurrent order placement (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC094: Verify database index on order_id for fast lookups (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC095: Verify daily backup job executes successfully (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC096: Verify order insertion into MongoDB collection (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC097: Verify Redis cache stores active menu items (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC098: Verify ACID transaction during concurrent order placement (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC099: Verify database index on order_id for fast lookups (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC100: Verify daily backup job executes successfully (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC101: Verify order insertion into MongoDB collection (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC102: Verify Redis cache stores active menu items (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC103: Verify ACID transaction during concurrent order placement (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC104: Verify database index on order_id for fast lookups (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC105: Verify daily backup job executes successfully (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC106: Verify order insertion into MongoDB collection (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC107: Verify Redis cache stores active menu items (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC108: Verify ACID transaction during concurrent order placement (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC109: Verify database index on order_id for fast lookups (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC110: Verify daily backup job executes successfully (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC111: Verify order insertion into MongoDB collection (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC112: Verify Redis cache stores active menu items (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC113: Verify ACID transaction during concurrent order placement (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC114: Verify database index on order_id for fast lookups (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC115: Verify daily backup job executes successfully (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC116: Verify order insertion into MongoDB collection (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC117: Verify Redis cache stores active menu items (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC118: Verify ACID transaction during concurrent order placement (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC119: Verify database index on order_id for fast lookups (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC120: Verify daily backup job executes successfully (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC121: Verify order insertion into MongoDB collection (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC122: Verify Redis cache stores active menu items (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC123: Verify ACID transaction during concurrent order placement (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC124: Verify database index on order_id for fast lookups (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC125: Verify daily backup job executes successfully (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC126: Verify order insertion into MongoDB collection (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC127: Verify Redis cache stores active menu items (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC128: Verify ACID transaction during concurrent order placement (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC129: Verify database index on order_id for fast lookups (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC130: Verify daily backup job executes successfully (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC131: Verify order insertion into MongoDB collection (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC132: Verify Redis cache stores active menu items (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC133: Verify ACID transaction during concurrent order placement (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC134: Verify database index on order_id for fast lookups (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC135: Verify daily backup job executes successfully (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC136: Verify order insertion into MongoDB collection (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC137: Verify Redis cache stores active menu items (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC138: Verify ACID transaction during concurrent order placement (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC139: Verify database index on order_id for fast lookups (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC140: Verify daily backup job executes successfully (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC141: Verify order insertion into MongoDB collection (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC142: Verify Redis cache stores active menu items (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC143: Verify ACID transaction during concurrent order placement (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC144: Verify database index on order_id for fast lookups (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC145: Verify daily backup job executes successfully (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC146: Verify order insertion into MongoDB collection (Scenario 30)</t>
+  </si>
+  <si>
+    <t>TC147: Verify Redis cache stores active menu items (Scenario 30)</t>
+  </si>
+  <si>
+    <t>TC148: Verify ACID transaction during concurrent order placement (Scenario 30)</t>
+  </si>
+  <si>
+    <t>TC149: Verify database index on order_id for fast lookups (Scenario 30)</t>
+  </si>
+  <si>
+    <t>TC150: Verify daily backup job executes successfully (Scenario 30)</t>
+  </si>
+  <si>
+    <t>External Integrations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC151: Verify Razorpay payment gateway webhook triggers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC152: Verify Firebase Cloud Messaging (FCM) push alerts </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC153: Verify Twilio SMS integration for OTP login </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC154: Verify AWS S3 upload for canteen item images </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC155: Verify Google Maps API for campus delivery distance </t>
+  </si>
+  <si>
+    <t>TC156: Verify Razorpay payment gateway webhook triggers (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC157: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC158: Verify Twilio SMS integration for OTP login (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC159: Verify AWS S3 upload for canteen item images (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC160: Verify Google Maps API for campus delivery distance (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC161: Verify Razorpay payment gateway webhook triggers (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC162: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC163: Verify Twilio SMS integration for OTP login (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC164: Verify AWS S3 upload for canteen item images (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC165: Verify Google Maps API for campus delivery distance (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC166: Verify Razorpay payment gateway webhook triggers (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC167: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC168: Verify Twilio SMS integration for OTP login (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC169: Verify AWS S3 upload for canteen item images (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC170: Verify Google Maps API for campus delivery distance (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC171: Verify Razorpay payment gateway webhook triggers (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC172: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC173: Verify Twilio SMS integration for OTP login (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC174: Verify AWS S3 upload for canteen item images (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC175: Verify Google Maps API for campus delivery distance (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC176: Verify Razorpay payment gateway webhook triggers (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC177: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC178: Verify Twilio SMS integration for OTP login (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC179: Verify AWS S3 upload for canteen item images (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC180: Verify Google Maps API for campus delivery distance (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC181: Verify Razorpay payment gateway webhook triggers (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC182: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC183: Verify Twilio SMS integration for OTP login (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC184: Verify AWS S3 upload for canteen item images (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC185: Verify Google Maps API for campus delivery distance (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC186: Verify Razorpay payment gateway webhook triggers (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC187: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC188: Verify Twilio SMS integration for OTP login (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC189: Verify AWS S3 upload for canteen item images (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC190: Verify Google Maps API for campus delivery distance (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC191: Verify Razorpay payment gateway webhook triggers (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC192: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC193: Verify Twilio SMS integration for OTP login (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC194: Verify AWS S3 upload for canteen item images (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC195: Verify Google Maps API for campus delivery distance (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC196: Verify Razorpay payment gateway webhook triggers (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC197: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC198: Verify Twilio SMS integration for OTP login (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC199: Verify AWS S3 upload for canteen item images (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC200: Verify Google Maps API for campus delivery distance (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC201: Verify Razorpay payment gateway webhook triggers (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC202: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC203: Verify Twilio SMS integration for OTP login (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC204: Verify AWS S3 upload for canteen item images (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC205: Verify Google Maps API for campus delivery distance (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC206: Verify Razorpay payment gateway webhook triggers (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC207: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC208: Verify Twilio SMS integration for OTP login (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC209: Verify AWS S3 upload for canteen item images (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC210: Verify Google Maps API for campus delivery distance (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC211: Verify Razorpay payment gateway webhook triggers (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC212: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC213: Verify Twilio SMS integration for OTP login (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC214: Verify AWS S3 upload for canteen item images (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC215: Verify Google Maps API for campus delivery distance (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC216: Verify Razorpay payment gateway webhook triggers (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC217: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC218: Verify Twilio SMS integration for OTP login (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC219: Verify AWS S3 upload for canteen item images (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC220: Verify Google Maps API for campus delivery distance (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC221: Verify Razorpay payment gateway webhook triggers (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC222: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC223: Verify Twilio SMS integration for OTP login (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC224: Verify AWS S3 upload for canteen item images (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC225: Verify Google Maps API for campus delivery distance (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC226: Verify Razorpay payment gateway webhook triggers (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC227: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC228: Verify Twilio SMS integration for OTP login (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC229: Verify AWS S3 upload for canteen item images (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC230: Verify Google Maps API for campus delivery distance (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC231: Verify Razorpay payment gateway webhook triggers (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC232: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC233: Verify Twilio SMS integration for OTP login (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC234: Verify AWS S3 upload for canteen item images (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC235: Verify Google Maps API for campus delivery distance (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC236: Verify Razorpay payment gateway webhook triggers (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC237: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC238: Verify Twilio SMS integration for OTP login (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC239: Verify AWS S3 upload for canteen item images (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC240: Verify Google Maps API for campus delivery distance (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC241: Verify Razorpay payment gateway webhook triggers (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC242: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC243: Verify Twilio SMS integration for OTP login (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC244: Verify AWS S3 upload for canteen item images (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC245: Verify Google Maps API for campus delivery distance (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC246: Verify Razorpay payment gateway webhook triggers (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC247: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC248: Verify Twilio SMS integration for OTP login (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC249: Verify AWS S3 upload for canteen item images (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC250: Verify Google Maps API for campus delivery distance (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC251: Verify Razorpay payment gateway webhook triggers (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC252: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC253: Verify Twilio SMS integration for OTP login (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC254: Verify AWS S3 upload for canteen item images (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC255: Verify Google Maps API for campus delivery distance (Scenario 21)</t>
+  </si>
+  <si>
+    <t>TC256: Verify Razorpay payment gateway webhook triggers (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC257: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC258: Verify Twilio SMS integration for OTP login (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC259: Verify AWS S3 upload for canteen item images (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC260: Verify Google Maps API for campus delivery distance (Scenario 22)</t>
+  </si>
+  <si>
+    <t>TC261: Verify Razorpay payment gateway webhook triggers (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC262: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC263: Verify Twilio SMS integration for OTP login (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC264: Verify AWS S3 upload for canteen item images (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC265: Verify Google Maps API for campus delivery distance (Scenario 23)</t>
+  </si>
+  <si>
+    <t>TC266: Verify Razorpay payment gateway webhook triggers (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC267: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC268: Verify Twilio SMS integration for OTP login (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC269: Verify AWS S3 upload for canteen item images (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC270: Verify Google Maps API for campus delivery distance (Scenario 24)</t>
+  </si>
+  <si>
+    <t>TC271: Verify Razorpay payment gateway webhook triggers (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC272: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC273: Verify Twilio SMS integration for OTP login (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC274: Verify AWS S3 upload for canteen item images (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC275: Verify Google Maps API for campus delivery distance (Scenario 25)</t>
+  </si>
+  <si>
+    <t>TC276: Verify Razorpay payment gateway webhook triggers (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC277: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC278: Verify Twilio SMS integration for OTP login (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC279: Verify AWS S3 upload for canteen item images (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC280: Verify Google Maps API for campus delivery distance (Scenario 26)</t>
+  </si>
+  <si>
+    <t>TC281: Verify Razorpay payment gateway webhook triggers (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC282: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC283: Verify Twilio SMS integration for OTP login (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC284: Verify AWS S3 upload for canteen item images (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC285: Verify Google Maps API for campus delivery distance (Scenario 27)</t>
+  </si>
+  <si>
+    <t>TC286: Verify Razorpay payment gateway webhook triggers (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC287: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC288: Verify Twilio SMS integration for OTP login (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC289: Verify AWS S3 upload for canteen item images (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC290: Verify Google Maps API for campus delivery distance (Scenario 28)</t>
+  </si>
+  <si>
+    <t>TC291: Verify Razorpay payment gateway webhook triggers (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC292: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC293: Verify Twilio SMS integration for OTP login (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC294: Verify AWS S3 upload for canteen item images (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC295: Verify Google Maps API for campus delivery distance (Scenario 29)</t>
+  </si>
+  <si>
+    <t>TC296: Verify Razorpay payment gateway webhook triggers (Scenario 30)</t>
+  </si>
+  <si>
+    <t>TC297: Verify Firebase Cloud Messaging (FCM) push alerts (Scenario 30)</t>
+  </si>
+  <si>
+    <t>TC298: Verify Twilio SMS integration for OTP login (Scenario 30)</t>
+  </si>
+  <si>
+    <t>TC299: Verify AWS S3 upload for canteen item images (Scenario 30)</t>
+  </si>
+  <si>
+    <t>TC300: Verify Google Maps API for campus delivery distance (Scenario 30)</t>
   </si>
 </sst>
 </file>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:12:20 AM</t>
+    <t>8/7/2026, 5:03:51 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:03:51 AM</t>
+    <t>8/7/2026, 5:11:56 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:11:56 AM</t>
+    <t>8/7/2026, 5:18:18 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:18:18 AM</t>
+    <t>8/7/2026, 5:20:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:20:04 AM</t>
+    <t>8/7/2026, 5:31:58 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:31:58 AM</t>
+    <t>8/7/2026, 5:38:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:38:04 AM</t>
+    <t>8/7/2026, 5:45:10 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:45:10 AM</t>
+    <t>8/7/2026, 5:55:52 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:55:52 AM</t>
+    <t>8/7/2026, 6:14:45 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:14:45 AM</t>
+    <t>8/7/2026, 6:20:07 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>

--- a/load-test-report.xlsx
+++ b/load-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:20:07 AM</t>
+    <t>8/7/2026, 6:30:06 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify Redis cache stores active menu items </t>
